--- a/Result/profitability/2427.xlsx
+++ b/Result/profitability/2427.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.03</v>
       </c>
       <c r="M2" t="n">
-        <v>0.305</v>
+        <v>0.34</v>
       </c>
       <c r="N2" t="n">
-        <v>28.33375</v>
+        <v>28.26125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -693,7 +693,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>97.09999999999999</v>
@@ -780,10 +780,10 @@
         <v>-0.23</v>
       </c>
       <c r="M3" t="n">
-        <v>0.25375</v>
+        <v>0.25875</v>
       </c>
       <c r="N3" t="n">
-        <v>26.50625</v>
+        <v>26.895</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2025</v>
+        <v>0.195</v>
       </c>
       <c r="N4" t="n">
-        <v>26.615</v>
+        <v>26.0575</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>0.22</v>
       </c>
       <c r="M5" t="n">
-        <v>0.165</v>
+        <v>0.245</v>
       </c>
       <c r="N5" t="n">
-        <v>26.00125</v>
+        <v>27.50375</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0.12625</v>
+        <v>0.15</v>
       </c>
       <c r="N6" t="n">
-        <v>27.29625</v>
+        <v>26.53375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.09375</v>
+        <v>0.09625000000000002</v>
       </c>
       <c r="N7" t="n">
-        <v>26.40375</v>
+        <v>28.275</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.18</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01750000000000001</v>
+        <v>0.03875000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>27.595</v>
+        <v>29.22125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         <v>-0.49</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.07875</v>
+        <v>-0.07874999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>28.005</v>
@@ -1774,7 +1774,7 @@
         <v>0.01</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.04625</v>
+        <v>-0.04624999999999999</v>
       </c>
       <c r="N11" t="n">
         <v>31.185</v>
@@ -1903,7 +1903,7 @@
         <v>0.09</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.03625</v>
+        <v>-0.03624999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>30.83875</v>
@@ -2030,7 +2030,7 @@
         <v>0.08</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.05375</v>
+        <v>-0.05374999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>30.4325</v>
@@ -9360,19 +9360,19 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>-33</v>
+        <v>-133</v>
       </c>
       <c r="J71" t="n">
-        <v>79</v>
+        <v>-22</v>
       </c>
       <c r="K71" t="n">
-        <v>64</v>
+        <v>-36</v>
       </c>
       <c r="L71" t="n">
-        <v>0.32</v>
+        <v>-0.18</v>
       </c>
       <c r="M71" t="n">
-        <v>0.37125</v>
+        <v>0.30875</v>
       </c>
       <c r="N71" t="n">
         <v>30.5775</v>
@@ -9396,16 +9396,16 @@
         <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V71" t="n">
         <v>114.2</v>
       </c>
       <c r="W71" t="n">
-        <v>-0.2</v>
+        <v>-0.7</v>
       </c>
       <c r="X71" t="n">
-        <v>-0.3846153846153846</v>
+        <v>-1.346153846153846</v>
       </c>
       <c r="Y71" t="n">
         <v>-16.48</v>
@@ -9414,10 +9414,10 @@
         <v>-0.4529961517317208</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.02000000000000002</v>
+        <v>-0.48</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.06666666666666665</v>
+        <v>-1.6</v>
       </c>
       <c r="AC71" t="n">
         <v>-18.29</v>
@@ -9429,7 +9429,7 @@
         <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>EPS成長 / 毛利率衰退</t>
+          <t>EPS衰退 / 毛利率衰退</t>
         </is>
       </c>
       <c r="AK71" t="n">
@@ -9487,52 +9487,52 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>24</v>
+        <v>124</v>
       </c>
       <c r="J72" t="n">
-        <v>62</v>
+        <v>162</v>
       </c>
       <c r="K72" t="n">
-        <v>51</v>
+        <v>152</v>
       </c>
       <c r="L72" t="n">
-        <v>0.26</v>
+        <v>0.77</v>
       </c>
       <c r="M72" t="n">
-        <v>0.3625</v>
+        <v>0.36375</v>
       </c>
       <c r="N72" t="n">
         <v>31.515</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P72" t="n">
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" t="n">
         <v>0</v>
       </c>
       <c r="U72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V72" t="n">
         <v>114.3</v>
       </c>
       <c r="W72" t="n">
-        <v>-0.06</v>
+        <v>0.95</v>
       </c>
       <c r="X72" t="n">
-        <v>-0.1875</v>
+        <v>-5.277777777777778</v>
       </c>
       <c r="Y72" t="n">
         <v>18.12</v>
@@ -9541,10 +9541,10 @@
         <v>0.9105527638190958</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.5900000000000001</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.4444444444444446</v>
+        <v>3.277777777777778</v>
       </c>
       <c r="AC72" t="n">
         <v>5.520000000000003</v>
@@ -9553,7 +9553,7 @@
         <v>0.169846153846154</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF72" t="n">
         <v>1</v>
@@ -9626,7 +9626,7 @@
         <v>0.43</v>
       </c>
       <c r="M73" t="n">
-        <v>0.37</v>
+        <v>0.37125</v>
       </c>
       <c r="N73" t="n">
         <v>29.31</v>
@@ -9650,16 +9650,16 @@
         <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V73" t="n">
         <v>114.4</v>
       </c>
       <c r="W73" t="n">
-        <v>0.17</v>
+        <v>-0.34</v>
       </c>
       <c r="X73" t="n">
-        <v>0.6538461538461537</v>
+        <v>-0.4415584415584416</v>
       </c>
       <c r="Y73" t="n">
         <v>-21.07</v>
@@ -9680,7 +9680,7 @@
         <v>-0.4116626171468241</v>
       </c>
       <c r="AE73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
         <v>1</v>
@@ -9753,7 +9753,7 @@
         <v>0.28</v>
       </c>
       <c r="M74" t="n">
-        <v>0.33875</v>
+        <v>0.34</v>
       </c>
       <c r="N74" t="n">
         <v>28.7075</v>
@@ -9777,7 +9777,7 @@
         <v>0</v>
       </c>
       <c r="U74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V74" t="n">
         <v>115.1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2427</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1253</v>
+      </c>
+      <c r="D75" t="n">
+        <v>853</v>
+      </c>
+      <c r="E75" t="n">
+        <v>400</v>
+      </c>
+      <c r="F75" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="G75" t="n">
+        <v>92</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.34%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>17</v>
+      </c>
+      <c r="J75" t="n">
+        <v>109</v>
+      </c>
+      <c r="K75" t="n">
+        <v>90</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>27.92375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.607142857142857</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.6879957694341619</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.6040201005025128</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
